--- a/artfynd/A 4219-2023 artfynd.xlsx
+++ b/artfynd/A 4219-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4219-2023 artfynd.xlsx
+++ b/artfynd/A 4219-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1483,6 +1483,112 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>112304489</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98971</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sydväst om Bergstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>580521</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6571103</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ingrid Nilsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ingrid Nilsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4219-2023 artfynd.xlsx
+++ b/artfynd/A 4219-2023 artfynd.xlsx
@@ -1488,7 +1488,7 @@
         <v>112304489</v>
       </c>
       <c r="B8" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 4219-2023 artfynd.xlsx
+++ b/artfynd/A 4219-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106540296</v>
+        <v>105992416</v>
       </c>
       <c r="B2" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,50 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergstorp , Srm</t>
+          <t>Bergstorp, Eriksnäs, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580536.9912547227</v>
+        <v>580480</v>
       </c>
       <c r="R2" t="n">
-        <v>6571106.725495513</v>
+        <v>6571136</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,22 +744,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-02-08</t>
+          <t>2023-01-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-02-08</t>
+          <t>2023-01-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Kudde om ca 40 cm hög, växande intill ett kärr med flera observationer av blåmossa i området.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,8 +773,19 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Barrblandskog med surdråg och kärr. Hög fuktighet.</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -800,59 +802,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107137723</v>
+        <v>105983079</v>
       </c>
       <c r="B3" t="n">
-        <v>89776</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6040162</v>
+        <v>4217</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergstorp, Berget, Bergstorp, Srm</t>
+          <t>Bergstorp, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580531.7578640198</v>
+        <v>580527</v>
       </c>
       <c r="R3" t="n">
-        <v>6571063.665557685</v>
+        <v>6571142</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,27 +868,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2023-01-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2023-01-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Växer på lång tallåga i kontinutitetsskog som nu är avverkningsanmäld.</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,64 +892,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrblandskog. Kontinutietsskog med hög fuktighet.</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Tre fruktkroppar på tallågan.</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tre fruktkroppar på tallågan.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107137892</v>
+        <v>108143951</v>
       </c>
       <c r="B4" t="n">
-        <v>89776</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,16 +921,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6040162</v>
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -987,26 +943,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergstorp, Berget, Bergstorp, Srm</t>
+          <t>Bergstorp , Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580530.430534999</v>
+        <v>580488</v>
       </c>
       <c r="R4" t="n">
-        <v>6571077.953795558</v>
+        <v>6571109</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1030,27 +987,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2023-04-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2023-04-13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>En fruktkropp på tallåga nära ett kärr. Skogen avverkningsanmäld</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,34 +1011,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrblandskog. KontinutItetsskog med hög fuktighet.</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1103,51 +1029,47 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>108063751</v>
+        <v>106540296</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1155,10 +1077,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580524.826035346</v>
+        <v>580537</v>
       </c>
       <c r="R5" t="n">
-        <v>6571124.874128077</v>
+        <v>6571107</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1185,27 +1107,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-04-12</t>
+          <t>2023-02-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-04-12</t>
+          <t>2023-02-08</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Knärotsplantor i avverkningsanmäld skog.</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1235,12 +1152,7 @@
         <v>108063292</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580535.9673266909</v>
+        <v>580536</v>
       </c>
       <c r="R6" t="n">
-        <v>6571106.703785046</v>
+        <v>6571107</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1361,51 +1273,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>108143951</v>
+        <v>108063751</v>
       </c>
       <c r="B7" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1413,13 +1320,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580488</v>
+        <v>580525</v>
       </c>
       <c r="R7" t="n">
-        <v>6571109</v>
+        <v>6571125</v>
       </c>
       <c r="S7" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1443,22 +1350,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-04-13</t>
+          <t>2023-04-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-04-13</t>
+          <t>2023-04-12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Knärotsplantor i avverkningsanmäld skog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1488,7 +1400,7 @@
         <v>112304489</v>
       </c>
       <c r="B8" t="n">
-        <v>99014</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1589,6 +1501,417 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>105978896</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bergstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>580527</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6571142</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kristina Bäck</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kristina Bäck</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>107137723</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bergstorp, Berget, Bergstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>580532</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6571064</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Växer på lång tallåga i kontinutitetsskog som nu är avverkningsanmäld.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Barrblandskog. Kontinutietsskog med hög fuktighet.</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Tre fruktkroppar på tallågan.</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tre fruktkroppar på tallågan.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>107137892</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bergstorp, Berget, Bergstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>580531</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6571078</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>En fruktkropp på tallåga nära ett kärr. Skogen avverkningsanmäld</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Barrblandskog. KontinutItetsskog med hög fuktighet.</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4219-2023 artfynd.xlsx
+++ b/artfynd/A 4219-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105992416</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105983079</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,6 +1041,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108143951</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1146,6 +1166,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106540296</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1270,6 +1295,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108063292</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1394,6 +1424,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108063751</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1500,6 +1535,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112304489</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1608,6 +1648,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105978896</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1762,6 +1807,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107137723</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1911,8 +1961,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107137892</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>